--- a/product-definitions/spreadsheet/n2o-sf6-concentration.xlsx
+++ b/product-definitions/spreadsheet/n2o-sf6-concentration.xlsx
@@ -207,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -241,11 +241,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -336,7 +331,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -1956,7 +1951,7 @@
       </c>
       <c r="G20" s="6"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6" t="s">
         <v>19</v>
@@ -1969,7 +1964,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
         <v>20</v>
@@ -1982,7 +1977,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>22</v>
@@ -1995,7 +1990,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
         <v>23</v>
@@ -2008,7 +2003,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
         <v>25</v>
@@ -2021,7 +2016,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>26</v>
@@ -2034,7 +2029,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
         <v>28</v>
@@ -2047,7 +2042,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="16" t="s">
         <v>30</v>
@@ -2060,7 +2055,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="8"/>
@@ -2069,7 +2064,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="11" t="s">
         <v>35</v>
       </c>
@@ -2080,7 +2075,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
         <v>10</v>
@@ -2093,7 +2088,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
         <v>12</v>
@@ -2106,7 +2101,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="7" t="s">
         <v>2</v>
@@ -2119,7 +2114,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6" t="s">
         <v>19</v>
@@ -2132,7 +2127,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6" t="s">
         <v>20</v>
@@ -2145,7 +2140,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="6" t="s">
         <v>22</v>
@@ -2158,7 +2153,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>23</v>
@@ -2171,7 +2166,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6"/>
       <c r="B38" s="6" t="s">
         <v>25</v>
@@ -2184,7 +2179,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="7" t="s">
         <v>26</v>
@@ -2197,7 +2192,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6" t="s">
         <v>28</v>
@@ -2210,7 +2205,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="16" t="s">
         <v>30</v>
@@ -2223,7 +2218,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2232,7 +2227,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>38</v>
       </c>
@@ -2243,7 +2238,7 @@
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
         <v>10</v>
@@ -2256,7 +2251,7 @@
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
         <v>12</v>
@@ -2269,7 +2264,7 @@
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="7"/>
       <c r="B46" s="7" t="s">
         <v>2</v>
@@ -2282,7 +2277,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
         <v>19</v>
@@ -2295,7 +2290,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
         <v>20</v>
@@ -2308,7 +2303,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
         <v>22</v>
@@ -2321,7 +2316,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
         <v>23</v>
@@ -2334,7 +2329,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
         <v>25</v>
@@ -2347,7 +2342,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
         <v>26</v>
@@ -2360,7 +2355,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
         <v>28</v>
@@ -2373,7 +2368,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="16" t="s">
         <v>30</v>
@@ -2386,10 +2381,10 @@
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="22"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
         <v>41</v>
       </c>
@@ -2399,7 +2394,7 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="6" t="s">
         <v>10</v>
@@ -2411,7 +2406,7 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>12</v>
@@ -2423,7 +2418,7 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="7" t="s">
         <v>2</v>
@@ -2437,7 +2432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
         <v>16</v>
@@ -2451,7 +2446,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
         <v>19</v>
@@ -2463,7 +2458,7 @@
       </c>
       <c r="F61" s="6"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
         <v>20</v>
@@ -2475,7 +2470,7 @@
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
         <v>22</v>
@@ -2487,7 +2482,7 @@
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
         <v>23</v>
@@ -2499,7 +2494,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
         <v>25</v>
@@ -2511,7 +2506,7 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="7" t="s">
         <v>26</v>
@@ -2523,7 +2518,7 @@
       </c>
       <c r="F66" s="6"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
         <v>28</v>
@@ -2535,7 +2530,7 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="16" t="s">
         <v>30</v>
@@ -2547,7 +2542,7 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2555,7 +2550,7 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
@@ -2565,7 +2560,7 @@
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6" t="s">
         <v>10</v>
@@ -2577,7 +2572,7 @@
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
         <v>12</v>
@@ -2589,7 +2584,7 @@
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="7" t="s">
         <v>2</v>
@@ -2603,7 +2598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6"/>
       <c r="B74" s="7" t="s">
         <v>16</v>
@@ -2617,7 +2612,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="6" t="s">
         <v>19</v>
@@ -2629,7 +2624,7 @@
       </c>
       <c r="F75" s="6"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="6" t="s">
         <v>20</v>
@@ -2641,7 +2636,7 @@
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
         <v>22</v>
@@ -2653,7 +2648,7 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6"/>
       <c r="B78" s="6" t="s">
         <v>23</v>
@@ -2665,7 +2660,7 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
         <v>25</v>
@@ -2677,7 +2672,7 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6"/>
       <c r="B80" s="7" t="s">
         <v>26</v>
@@ -2689,7 +2684,7 @@
       </c>
       <c r="F80" s="6"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6"/>
       <c r="B81" s="6" t="s">
         <v>28</v>
@@ -2701,7 +2696,7 @@
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="16" t="s">
         <v>30</v>
@@ -2713,7 +2708,7 @@
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="8"/>
@@ -2721,7 +2716,7 @@
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="11" t="s">
         <v>46</v>
       </c>
@@ -2731,7 +2726,7 @@
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="6" t="s">
         <v>10</v>
@@ -2743,7 +2738,7 @@
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="6" t="s">
         <v>12</v>
@@ -2755,7 +2750,7 @@
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="7"/>
       <c r="B87" s="7" t="s">
         <v>2</v>
@@ -2767,7 +2762,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="6" t="s">
         <v>19</v>
@@ -2779,7 +2774,7 @@
       </c>
       <c r="F88" s="6"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="6" t="s">
         <v>20</v>
@@ -2791,7 +2786,7 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="6" t="s">
         <v>22</v>
@@ -2803,7 +2798,7 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6"/>
       <c r="B91" s="6" t="s">
         <v>23</v>
@@ -2815,7 +2810,7 @@
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
         <v>25</v>
@@ -2827,7 +2822,7 @@
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="7" t="s">
         <v>26</v>
@@ -2839,7 +2834,7 @@
       </c>
       <c r="F93" s="6"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
         <v>28</v>
@@ -2851,7 +2846,7 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="16" t="s">
         <v>30</v>
@@ -2863,7 +2858,7 @@
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -2871,7 +2866,7 @@
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="11" t="s">
         <v>48</v>
       </c>
@@ -2881,7 +2876,7 @@
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6"/>
       <c r="B98" s="6" t="s">
         <v>10</v>
@@ -2893,7 +2888,7 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
         <v>12</v>
@@ -2905,7 +2900,7 @@
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
         <v>2</v>
@@ -2917,7 +2912,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
         <v>19</v>
@@ -2929,7 +2924,7 @@
       </c>
       <c r="F101" s="6"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="6" t="s">
         <v>20</v>
@@ -2941,7 +2936,7 @@
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="6" t="s">
         <v>22</v>
@@ -2953,7 +2948,7 @@
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="6" t="s">
         <v>23</v>
@@ -2965,7 +2960,7 @@
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="6" t="s">
         <v>25</v>
@@ -2977,7 +2972,7 @@
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="7" t="s">
         <v>26</v>
@@ -2989,7 +2984,7 @@
       </c>
       <c r="F106" s="6"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6"/>
       <c r="B107" s="6" t="s">
         <v>28</v>
@@ -3001,7 +2996,7 @@
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6"/>
       <c r="B108" s="16" t="s">
         <v>30</v>
@@ -3013,17 +3008,17 @@
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="C109" s="22"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="24"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2" t="s">
         <v>10</v>
@@ -3032,7 +3027,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2" t="s">
         <v>12</v>
@@ -3041,7 +3036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2" t="s">
         <v>2</v>
@@ -3050,14 +3045,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C114" s="25"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
         <v>20</v>
@@ -3066,7 +3061,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="6" t="s">
         <v>53</v>
@@ -3075,7 +3070,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="8" t="s">
         <v>55</v>
@@ -3084,19 +3079,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="26"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="23" t="s">
         <v>57</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="24"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
         <v>10</v>
@@ -3105,7 +3100,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
         <v>12</v>
@@ -3114,7 +3109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
         <v>2</v>
@@ -3123,14 +3118,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C123" s="25"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
         <v>20</v>
@@ -3139,7 +3134,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="6" t="s">
         <v>53</v>
@@ -3148,7 +3143,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="8" t="s">
         <v>55</v>
